--- a/samples/charts/sbk-file-rocksdb-read.xlsx
+++ b/samples/charts/sbk-file-rocksdb-read.xlsx
@@ -32987,7 +32987,7 @@
       </c>
       <c r="H8" s="15" t="inlineStr">
         <is>
-          <t>4.26.6.3</t>
+          <t>4.26.7.1</t>
         </is>
       </c>
     </row>
@@ -33009,7 +33009,7 @@
       </c>
       <c r="H10" s="18" t="inlineStr">
         <is>
-          <t>19:53:41</t>
+          <t>20:06:09</t>
         </is>
       </c>
     </row>
